--- a/rag/eval/results_full150/statistical_tests_full150.xlsx
+++ b/rag/eval/results_full150/statistical_tests_full150.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Table3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,7 +507,7 @@
         <v>0.001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G2" t="n">
         <v>0.903</v>
@@ -516,7 +516,7 @@
         <v>0.114</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0706</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>0.00429</v>
@@ -547,7 +547,7 @@
         <v>0.00146</v>
       </c>
       <c r="F3" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G3" t="n">
         <v>0.903</v>
@@ -556,7 +556,7 @@
         <v>0.114</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0706</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>0.00626</v>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0105</v>
+        <v>0.0112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G4" t="n">
         <v>0.88</v>
@@ -599,7 +599,7 @@
         <v>0.0833</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0274</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="5">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0243</v>
+        <v>0.0259</v>
       </c>
       <c r="F5" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G5" t="n">
         <v>0.88</v>
@@ -639,7 +639,7 @@
         <v>0.0833</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0486</v>
+        <v>0.0518</v>
       </c>
     </row>
     <row r="6">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.386</v>
+        <v>0.412</v>
       </c>
       <c r="F6" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G6" t="n">
         <v>0.845</v>
@@ -679,7 +679,7 @@
         <v>0.102</v>
       </c>
       <c r="J6" t="n">
-        <v>0.445</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="7">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.348</v>
+        <v>0.362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G7" t="n">
         <v>0.845</v>
@@ -719,7 +719,7 @@
         <v>0.102</v>
       </c>
       <c r="J7" t="n">
-        <v>0.402</v>
+        <v>0.418</v>
       </c>
     </row>
     <row r="8">
@@ -744,22 +744,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.3e-05</v>
+        <v>6.210000000000001e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G8" t="n">
-        <v>0.695</v>
+        <v>0.696</v>
       </c>
       <c r="H8" t="n">
         <v>0.114</v>
       </c>
       <c r="I8" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000472</v>
+        <v>0.000466</v>
       </c>
     </row>
     <row r="9">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0005820000000000001</v>
+        <v>0.000581</v>
       </c>
       <c r="F9" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G9" t="n">
-        <v>0.695</v>
+        <v>0.696</v>
       </c>
       <c r="H9" t="n">
         <v>0.114</v>
       </c>
       <c r="I9" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="J9" t="n">
         <v>0.00317</v>
@@ -824,22 +824,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.93e-05</v>
+        <v>1.85e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H10" t="n">
         <v>0.114</v>
       </c>
       <c r="I10" t="n">
-        <v>0.148</v>
+        <v>0.147</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000232</v>
+        <v>0.000222</v>
       </c>
     </row>
     <row r="11">
@@ -867,16 +867,16 @@
         <v>0.000435</v>
       </c>
       <c r="F11" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>0.114</v>
       </c>
       <c r="I11" t="n">
-        <v>0.148</v>
+        <v>0.147</v>
       </c>
       <c r="J11" t="n">
         <v>0.00261</v>
@@ -999,7 +999,7 @@
         <v>0.109</v>
       </c>
       <c r="J14" t="n">
-        <v>0.23</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="15">
@@ -1039,7 +1039,7 @@
         <v>0.109</v>
       </c>
       <c r="J15" t="n">
-        <v>0.479</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="16">
@@ -1079,7 +1079,7 @@
         <v>0.0791</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0269</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="17">
@@ -1119,7 +1119,7 @@
         <v>0.0791</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0225</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="18">
@@ -1144,13 +1144,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.154</v>
+        <v>0.192</v>
       </c>
       <c r="F18" t="n">
         <v>0.799</v>
       </c>
       <c r="G18" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="H18" t="n">
         <v>0.154</v>
@@ -1159,7 +1159,7 @@
         <v>0.131</v>
       </c>
       <c r="J18" t="n">
-        <v>0.215</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="19">
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.109</v>
+        <v>0.133</v>
       </c>
       <c r="F19" t="n">
         <v>0.799</v>
       </c>
       <c r="G19" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="H19" t="n">
         <v>0.154</v>
@@ -1199,7 +1199,7 @@
         <v>0.131</v>
       </c>
       <c r="J19" t="n">
-        <v>0.164</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="20">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.536</v>
+        <v>0.595</v>
       </c>
       <c r="F20" t="n">
         <v>0.799</v>
       </c>
       <c r="G20" t="n">
-        <v>0.788</v>
+        <v>0.79</v>
       </c>
       <c r="H20" t="n">
         <v>0.154</v>
@@ -1239,7 +1239,7 @@
         <v>0.131</v>
       </c>
       <c r="J20" t="n">
-        <v>0.585</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="21">
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F21" t="n">
         <v>0.799</v>
       </c>
       <c r="G21" t="n">
-        <v>0.788</v>
+        <v>0.79</v>
       </c>
       <c r="H21" t="n">
         <v>0.154</v>
@@ -1279,7 +1279,7 @@
         <v>0.131</v>
       </c>
       <c r="J21" t="n">
-        <v>0.632</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="22">
@@ -1439,7 +1439,7 @@
         <v>0.106</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0254</v>
+        <v>0.0245</v>
       </c>
     </row>
     <row r="26">
@@ -1464,13 +1464,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.947</v>
+        <v>0.93</v>
       </c>
       <c r="F26" t="n">
         <v>0.781</v>
       </c>
       <c r="G26" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="H26" t="n">
         <v>0.129</v>
@@ -1479,7 +1479,7 @@
         <v>0.11</v>
       </c>
       <c r="J26" t="n">
-        <v>0.947</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="27">
@@ -1510,7 +1510,7 @@
         <v>0.781</v>
       </c>
       <c r="G27" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="H27" t="n">
         <v>0.129</v>
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0186</v>
+        <v>0.0196</v>
       </c>
       <c r="F28" t="n">
         <v>0.781</v>
       </c>
       <c r="G28" t="n">
-        <v>0.714</v>
+        <v>0.715</v>
       </c>
       <c r="H28" t="n">
         <v>0.129</v>
@@ -1559,7 +1559,7 @@
         <v>0.156</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0399</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="29">
@@ -1590,7 +1590,7 @@
         <v>0.781</v>
       </c>
       <c r="G29" t="n">
-        <v>0.714</v>
+        <v>0.715</v>
       </c>
       <c r="H29" t="n">
         <v>0.129</v>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0333</v>
+        <v>0.0349</v>
       </c>
       <c r="F30" t="n">
         <v>0.781</v>
       </c>
       <c r="G30" t="n">
-        <v>0.715</v>
+        <v>0.717</v>
       </c>
       <c r="H30" t="n">
         <v>0.129</v>
@@ -1639,7 +1639,7 @@
         <v>0.153</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0624</v>
+        <v>0.0635</v>
       </c>
     </row>
     <row r="31">
@@ -1670,7 +1670,7 @@
         <v>0.781</v>
       </c>
       <c r="G31" t="n">
-        <v>0.715</v>
+        <v>0.717</v>
       </c>
       <c r="H31" t="n">
         <v>0.129</v>
@@ -1679,7 +1679,7 @@
         <v>0.153</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0615</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="32">
@@ -1719,7 +1719,7 @@
         <v>0.0584</v>
       </c>
       <c r="J32" t="n">
-        <v>0.144</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="33">
@@ -1759,7 +1759,7 @@
         <v>0.0584</v>
       </c>
       <c r="J33" t="n">
-        <v>0.271</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="34">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.802</v>
+        <v>0.8</v>
       </c>
       <c r="F34" t="n">
         <v>0.864</v>
@@ -1799,7 +1799,7 @@
         <v>0.11</v>
       </c>
       <c r="J34" t="n">
-        <v>0.83</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="35">
@@ -1839,7 +1839,7 @@
         <v>0.11</v>
       </c>
       <c r="J35" t="n">
-        <v>0.504</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="36">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0244</v>
+        <v>0.0242</v>
       </c>
       <c r="F36" t="n">
         <v>0.864</v>
@@ -1879,7 +1879,7 @@
         <v>0.191</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0472</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="37">
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.78e-06</v>
+        <v>1.9e-06</v>
       </c>
       <c r="F38" t="n">
         <v>0.864</v>
       </c>
       <c r="G38" t="n">
-        <v>0.597</v>
+        <v>0.598</v>
       </c>
       <c r="H38" t="n">
         <v>0.163</v>
@@ -1959,7 +1959,7 @@
         <v>0.215</v>
       </c>
       <c r="J38" t="n">
-        <v>2.67e-05</v>
+        <v>2.85e-05</v>
       </c>
     </row>
     <row r="39">
@@ -1990,7 +1990,7 @@
         <v>0.864</v>
       </c>
       <c r="G39" t="n">
-        <v>0.597</v>
+        <v>0.598</v>
       </c>
       <c r="H39" t="n">
         <v>0.163</v>
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5.86e-07</v>
+        <v>6.09e-07</v>
       </c>
       <c r="F40" t="n">
         <v>0.864</v>
       </c>
       <c r="G40" t="n">
-        <v>0.592</v>
+        <v>0.593</v>
       </c>
       <c r="H40" t="n">
         <v>0.163</v>
@@ -2039,7 +2039,7 @@
         <v>0.202</v>
       </c>
       <c r="J40" t="n">
-        <v>1.17e-05</v>
+        <v>1.22e-05</v>
       </c>
     </row>
     <row r="41">
@@ -2070,7 +2070,7 @@
         <v>0.864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.592</v>
+        <v>0.593</v>
       </c>
       <c r="H41" t="n">
         <v>0.163</v>
@@ -2279,7 +2279,7 @@
         <v>0.164</v>
       </c>
       <c r="J46" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="47">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.000647</v>
+        <v>0.000679</v>
       </c>
       <c r="F48" t="n">
         <v>0.793</v>
@@ -2356,10 +2356,10 @@
         <v>0.205</v>
       </c>
       <c r="I48" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="J48" t="n">
-        <v>0.00324</v>
+        <v>0.0034</v>
       </c>
     </row>
     <row r="49">
@@ -2396,7 +2396,7 @@
         <v>0.205</v>
       </c>
       <c r="I49" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="J49" t="n">
         <v>0.000785</v>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.0221</v>
+        <v>0.0229</v>
       </c>
       <c r="F50" t="n">
         <v>0.793</v>
@@ -2436,10 +2436,10 @@
         <v>0.205</v>
       </c>
       <c r="I50" t="n">
-        <v>0.177</v>
+        <v>0.178</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0457</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="51">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0131</v>
+        <v>0.0155</v>
       </c>
       <c r="F51" t="n">
         <v>0.793</v>
@@ -2476,10 +2476,10 @@
         <v>0.205</v>
       </c>
       <c r="I51" t="n">
-        <v>0.177</v>
+        <v>0.178</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0273</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="52">
@@ -2519,7 +2519,7 @@
         <v>0.172</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0472</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="53">
@@ -2559,7 +2559,7 @@
         <v>0.172</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0668</v>
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5.71e-05</v>
+        <v>5.82e-05</v>
       </c>
       <c r="F56" t="n">
         <v>0.778</v>
@@ -2679,7 +2679,7 @@
         <v>0.205</v>
       </c>
       <c r="J56" t="n">
-        <v>0.000472</v>
+        <v>0.000466</v>
       </c>
     </row>
     <row r="57">
@@ -2744,13 +2744,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.66e-07</v>
+        <v>1.65e-07</v>
       </c>
       <c r="F58" t="n">
         <v>0.778</v>
       </c>
       <c r="G58" t="n">
-        <v>0.625</v>
+        <v>0.626</v>
       </c>
       <c r="H58" t="n">
         <v>0.214</v>
@@ -2759,7 +2759,7 @@
         <v>0.225</v>
       </c>
       <c r="J58" t="n">
-        <v>9.96e-06</v>
+        <v>9.9e-06</v>
       </c>
     </row>
     <row r="59">
@@ -2790,7 +2790,7 @@
         <v>0.778</v>
       </c>
       <c r="G59" t="n">
-        <v>0.625</v>
+        <v>0.626</v>
       </c>
       <c r="H59" t="n">
         <v>0.214</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.43e-07</v>
+        <v>4.09e-07</v>
       </c>
       <c r="F60" t="n">
         <v>0.778</v>
@@ -2839,7 +2839,7 @@
         <v>0.223</v>
       </c>
       <c r="J60" t="n">
-        <v>1.17e-05</v>
+        <v>1.22e-05</v>
       </c>
     </row>
     <row r="61">
@@ -2907,7 +2907,7 @@
         <v>0.011</v>
       </c>
       <c r="F62" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G62" t="n">
         <v>0.845</v>
@@ -2919,7 +2919,7 @@
         <v>0.137</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="63">
@@ -2947,7 +2947,7 @@
         <v>0.0132</v>
       </c>
       <c r="F63" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G63" t="n">
         <v>0.845</v>
@@ -2959,7 +2959,7 @@
         <v>0.137</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0273</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="64">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.119</v>
+        <v>0.124</v>
       </c>
       <c r="F64" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G64" t="n">
         <v>0.8179999999999999</v>
@@ -2999,7 +2999,7 @@
         <v>0.185</v>
       </c>
       <c r="J64" t="n">
-        <v>0.174</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="65">
@@ -3027,7 +3027,7 @@
         <v>0.112</v>
       </c>
       <c r="F65" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G65" t="n">
         <v>0.8179999999999999</v>
@@ -3039,7 +3039,7 @@
         <v>0.185</v>
       </c>
       <c r="J65" t="n">
-        <v>0.164</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="66">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.262</v>
+        <v>0.273</v>
       </c>
       <c r="F66" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G66" t="n">
         <v>0.8</v>
@@ -3079,7 +3079,7 @@
         <v>0.224</v>
       </c>
       <c r="J66" t="n">
-        <v>0.314</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="67">
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.221</v>
+        <v>0.198</v>
       </c>
       <c r="F67" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G67" t="n">
         <v>0.8</v>
@@ -3119,7 +3119,7 @@
         <v>0.224</v>
       </c>
       <c r="J67" t="n">
-        <v>0.271</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="68">
@@ -3144,22 +3144,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.277</v>
+        <v>0.232</v>
       </c>
       <c r="F68" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G68" t="n">
-        <v>0.803</v>
+        <v>0.806</v>
       </c>
       <c r="H68" t="n">
         <v>0.164</v>
       </c>
       <c r="I68" t="n">
-        <v>0.21</v>
+        <v>0.206</v>
       </c>
       <c r="J68" t="n">
-        <v>0.326</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="69">
@@ -3184,22 +3184,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.331</v>
+        <v>0.245</v>
       </c>
       <c r="F69" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G69" t="n">
-        <v>0.803</v>
+        <v>0.806</v>
       </c>
       <c r="H69" t="n">
         <v>0.164</v>
       </c>
       <c r="I69" t="n">
-        <v>0.21</v>
+        <v>0.206</v>
       </c>
       <c r="J69" t="n">
-        <v>0.389</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="70">
@@ -3224,22 +3224,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.165</v>
+        <v>0.139</v>
       </c>
       <c r="F70" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H70" t="n">
         <v>0.164</v>
       </c>
       <c r="I70" t="n">
-        <v>0.199</v>
+        <v>0.196</v>
       </c>
       <c r="J70" t="n">
-        <v>0.22</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="71">
@@ -3267,16 +3267,16 @@
         <v>0.158</v>
       </c>
       <c r="F71" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H71" t="n">
         <v>0.164</v>
       </c>
       <c r="I71" t="n">
-        <v>0.199</v>
+        <v>0.196</v>
       </c>
       <c r="J71" t="n">
         <v>0.212</v>
@@ -3319,7 +3319,7 @@
         <v>0.164</v>
       </c>
       <c r="J72" t="n">
-        <v>0.165</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="73">
@@ -3439,7 +3439,7 @@
         <v>0.212</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0225</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="76">
@@ -3544,22 +3544,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.879</v>
       </c>
       <c r="F78" t="n">
         <v>0.758</v>
       </c>
       <c r="G78" t="n">
-        <v>0.761</v>
+        <v>0.764</v>
       </c>
       <c r="H78" t="n">
         <v>0.184</v>
       </c>
       <c r="I78" t="n">
-        <v>0.21</v>
+        <v>0.208</v>
       </c>
       <c r="J78" t="n">
-        <v>0.947</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="79">
@@ -3584,22 +3584,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.47</v>
+        <v>0.331</v>
       </c>
       <c r="F79" t="n">
         <v>0.758</v>
       </c>
       <c r="G79" t="n">
-        <v>0.761</v>
+        <v>0.764</v>
       </c>
       <c r="H79" t="n">
         <v>0.184</v>
       </c>
       <c r="I79" t="n">
-        <v>0.21</v>
+        <v>0.208</v>
       </c>
       <c r="J79" t="n">
-        <v>0.504</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="80">
@@ -3624,22 +3624,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="F80" t="n">
         <v>0.758</v>
       </c>
       <c r="G80" t="n">
-        <v>0.775</v>
+        <v>0.778</v>
       </c>
       <c r="H80" t="n">
         <v>0.184</v>
       </c>
       <c r="I80" t="n">
-        <v>0.196</v>
+        <v>0.193</v>
       </c>
       <c r="J80" t="n">
-        <v>0.735</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="81">
@@ -3664,22 +3664,22 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.463</v>
+        <v>0.422</v>
       </c>
       <c r="F81" t="n">
         <v>0.758</v>
       </c>
       <c r="G81" t="n">
-        <v>0.775</v>
+        <v>0.778</v>
       </c>
       <c r="H81" t="n">
         <v>0.184</v>
       </c>
       <c r="I81" t="n">
-        <v>0.196</v>
+        <v>0.193</v>
       </c>
       <c r="J81" t="n">
-        <v>0.504</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="82">
@@ -3864,13 +3864,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3.1e-05</v>
+        <v>2.77e-05</v>
       </c>
       <c r="F86" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>0.842</v>
+        <v>0.843</v>
       </c>
       <c r="H86" t="n">
         <v>0.178</v>
@@ -3879,7 +3879,7 @@
         <v>0.173</v>
       </c>
       <c r="J86" t="n">
-        <v>0.00031</v>
+        <v>0.000277</v>
       </c>
     </row>
     <row r="87">
@@ -3910,7 +3910,7 @@
         <v>0.6860000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>0.842</v>
+        <v>0.843</v>
       </c>
       <c r="H87" t="n">
         <v>0.178</v>
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0393</v>
+        <v>0.0322</v>
       </c>
       <c r="F88" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>0.774</v>
+        <v>0.777</v>
       </c>
       <c r="H88" t="n">
         <v>0.178</v>
       </c>
       <c r="I88" t="n">
-        <v>0.211</v>
+        <v>0.209</v>
       </c>
       <c r="J88" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="89">
@@ -3984,22 +3984,22 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.0386</v>
+        <v>0.029</v>
       </c>
       <c r="F89" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="G89" t="n">
-        <v>0.774</v>
+        <v>0.777</v>
       </c>
       <c r="H89" t="n">
         <v>0.178</v>
       </c>
       <c r="I89" t="n">
-        <v>0.211</v>
+        <v>0.209</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0702</v>
+        <v>0.0561</v>
       </c>
     </row>
     <row r="90">
@@ -4024,22 +4024,22 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.00997</v>
+        <v>0.00776</v>
       </c>
       <c r="F90" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>0.793</v>
+        <v>0.796</v>
       </c>
       <c r="H90" t="n">
         <v>0.178</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2</v>
+        <v>0.198</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0272</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="91">
@@ -4064,22 +4064,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.011</v>
+        <v>0.009010000000000001</v>
       </c>
       <c r="F91" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="G91" t="n">
-        <v>0.793</v>
+        <v>0.796</v>
       </c>
       <c r="H91" t="n">
         <v>0.178</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2</v>
+        <v>0.198</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0254</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="92">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.00335</v>
+        <v>0.00336</v>
       </c>
       <c r="F92" t="n">
         <v>0.799</v>
@@ -4113,13 +4113,13 @@
         <v>0.875</v>
       </c>
       <c r="H92" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I92" t="n">
         <v>0.0921</v>
       </c>
       <c r="J92" t="n">
-        <v>0.0118</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="93">
@@ -4153,7 +4153,7 @@
         <v>0.875</v>
       </c>
       <c r="H93" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I93" t="n">
         <v>0.0921</v>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.205</v>
+        <v>0.211</v>
       </c>
       <c r="F94" t="n">
         <v>0.799</v>
@@ -4193,13 +4193,13 @@
         <v>0.832</v>
       </c>
       <c r="H94" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I94" t="n">
         <v>0.15</v>
       </c>
       <c r="J94" t="n">
-        <v>0.262</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="95">
@@ -4233,7 +4233,7 @@
         <v>0.832</v>
       </c>
       <c r="H95" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I95" t="n">
         <v>0.15</v>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.5</v>
+        <v>0.487</v>
       </c>
       <c r="F96" t="n">
         <v>0.799</v>
@@ -4273,13 +4273,13 @@
         <v>0.782</v>
       </c>
       <c r="H96" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I96" t="n">
         <v>0.188</v>
       </c>
       <c r="J96" t="n">
-        <v>0.556</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="97">
@@ -4313,7 +4313,7 @@
         <v>0.782</v>
       </c>
       <c r="H97" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I97" t="n">
         <v>0.188</v>
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.000292</v>
+        <v>0.000298</v>
       </c>
       <c r="F98" t="n">
         <v>0.799</v>
       </c>
       <c r="G98" t="n">
-        <v>0.658</v>
+        <v>0.66</v>
       </c>
       <c r="H98" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I98" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="J98" t="n">
-        <v>0.00175</v>
+        <v>0.00179</v>
       </c>
     </row>
     <row r="99">
@@ -4390,13 +4390,13 @@
         <v>0.799</v>
       </c>
       <c r="G99" t="n">
-        <v>0.658</v>
+        <v>0.66</v>
       </c>
       <c r="H99" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I99" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="J99" t="n">
         <v>0.00261</v>
@@ -4424,22 +4424,22 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.00022</v>
+        <v>0.000218</v>
       </c>
       <c r="F100" t="n">
         <v>0.799</v>
       </c>
       <c r="G100" t="n">
-        <v>0.658</v>
+        <v>0.66</v>
       </c>
       <c r="H100" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I100" t="n">
         <v>0.172</v>
       </c>
       <c r="J100" t="n">
-        <v>0.00147</v>
+        <v>0.00145</v>
       </c>
     </row>
     <row r="101">
@@ -4470,10 +4470,10 @@
         <v>0.799</v>
       </c>
       <c r="G101" t="n">
-        <v>0.658</v>
+        <v>0.66</v>
       </c>
       <c r="H101" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="I101" t="n">
         <v>0.172</v>
@@ -4679,7 +4679,7 @@
         <v>0.145</v>
       </c>
       <c r="J106" t="n">
-        <v>0.0245</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="107">
@@ -4744,22 +4744,22 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.0887</v>
+        <v>0.112</v>
       </c>
       <c r="F108" t="n">
         <v>0.758</v>
       </c>
       <c r="G108" t="n">
-        <v>0.722</v>
+        <v>0.724</v>
       </c>
       <c r="H108" t="n">
         <v>0.169</v>
       </c>
       <c r="I108" t="n">
-        <v>0.167</v>
+        <v>0.168</v>
       </c>
       <c r="J108" t="n">
-        <v>0.144</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="109">
@@ -4784,22 +4784,22 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="F109" t="n">
         <v>0.758</v>
       </c>
       <c r="G109" t="n">
-        <v>0.722</v>
+        <v>0.724</v>
       </c>
       <c r="H109" t="n">
         <v>0.169</v>
       </c>
       <c r="I109" t="n">
-        <v>0.167</v>
+        <v>0.168</v>
       </c>
       <c r="J109" t="n">
-        <v>0.117</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="110">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.478</v>
+        <v>0.536</v>
       </c>
       <c r="F110" t="n">
         <v>0.758</v>
       </c>
       <c r="G110" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="H110" t="n">
         <v>0.169</v>
@@ -4839,7 +4839,7 @@
         <v>0.158</v>
       </c>
       <c r="J110" t="n">
-        <v>0.541</v>
+        <v>0.596</v>
       </c>
     </row>
     <row r="111">
@@ -4864,13 +4864,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.323</v>
+        <v>0.433</v>
       </c>
       <c r="F111" t="n">
         <v>0.758</v>
       </c>
       <c r="G111" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="H111" t="n">
         <v>0.169</v>
@@ -4879,7 +4879,7 @@
         <v>0.158</v>
       </c>
       <c r="J111" t="n">
-        <v>0.388</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="112">
@@ -5064,13 +5064,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.247</v>
+        <v>0.238</v>
       </c>
       <c r="F116" t="n">
         <v>0.711</v>
       </c>
       <c r="G116" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="H116" t="n">
         <v>0.152</v>
@@ -5079,7 +5079,7 @@
         <v>0.176</v>
       </c>
       <c r="J116" t="n">
-        <v>0.302</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="117">
@@ -5110,7 +5110,7 @@
         <v>0.711</v>
       </c>
       <c r="G117" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="H117" t="n">
         <v>0.152</v>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.132</v>
+        <v>0.142</v>
       </c>
       <c r="F118" t="n">
         <v>0.711</v>
       </c>
       <c r="G118" t="n">
-        <v>0.667</v>
+        <v>0.669</v>
       </c>
       <c r="H118" t="n">
         <v>0.152</v>
@@ -5159,7 +5159,7 @@
         <v>0.194</v>
       </c>
       <c r="J118" t="n">
-        <v>0.189</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="119">
@@ -5190,7 +5190,7 @@
         <v>0.711</v>
       </c>
       <c r="G119" t="n">
-        <v>0.667</v>
+        <v>0.669</v>
       </c>
       <c r="H119" t="n">
         <v>0.152</v>
@@ -5199,7 +5199,7 @@
         <v>0.194</v>
       </c>
       <c r="J119" t="n">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="120">
@@ -5224,13 +5224,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.215</v>
+        <v>0.229</v>
       </c>
       <c r="F120" t="n">
         <v>0.711</v>
       </c>
       <c r="G120" t="n">
-        <v>0.674</v>
+        <v>0.675</v>
       </c>
       <c r="H120" t="n">
         <v>0.152</v>
@@ -5239,7 +5239,7 @@
         <v>0.195</v>
       </c>
       <c r="J120" t="n">
-        <v>0.269</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="121">
@@ -5264,13 +5264,13 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.191</v>
+        <v>0.233</v>
       </c>
       <c r="F121" t="n">
         <v>0.711</v>
       </c>
       <c r="G121" t="n">
-        <v>0.674</v>
+        <v>0.675</v>
       </c>
       <c r="H121" t="n">
         <v>0.152</v>
@@ -5279,7 +5279,7 @@
         <v>0.195</v>
       </c>
       <c r="J121" t="n">
-        <v>0.249</v>
+        <v>0.285</v>
       </c>
     </row>
   </sheetData>
@@ -5701,16 +5701,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.853</v>
+        <v>0.86</v>
       </c>
       <c r="G11" t="n">
-        <v>0.873</v>
+        <v>0.88</v>
       </c>
       <c r="H11" t="n">
-        <v>0.737</v>
+        <v>0.732</v>
       </c>
       <c r="I11" t="n">
-        <v>0.85</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="12">
@@ -6293,10 +6293,10 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="G27" t="n">
-        <v>0.931</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -6885,16 +6885,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="G43" t="n">
-        <v>0.827</v>
+        <v>0.84</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.862</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="44">
@@ -7477,16 +7477,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.853</v>
+        <v>0.861</v>
       </c>
       <c r="G59" t="n">
-        <v>0.876</v>
+        <v>0.883</v>
       </c>
       <c r="H59" t="n">
-        <v>0.616</v>
+        <v>0.609</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="60">
@@ -8069,16 +8069,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.853</v>
+        <v>0.86</v>
       </c>
       <c r="G75" t="n">
         <v>0.893</v>
       </c>
       <c r="H75" t="n">
-        <v>0.386</v>
+        <v>0.483</v>
       </c>
       <c r="I75" t="n">
-        <v>0.643</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="76">
@@ -8661,7 +8661,7 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="G91" t="n">
         <v>0.9330000000000001</v>
@@ -9253,16 +9253,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="G107" t="n">
         <v>0.864</v>
       </c>
       <c r="H107" t="n">
-        <v>0.299</v>
+        <v>0.399</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="108">
@@ -9845,16 +9845,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.853</v>
+        <v>0.861</v>
       </c>
       <c r="G123" t="n">
         <v>0.897</v>
       </c>
       <c r="H123" t="n">
-        <v>0.299</v>
+        <v>0.382</v>
       </c>
       <c r="I123" t="n">
-        <v>0.498</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="124">
@@ -10437,16 +10437,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.853</v>
+        <v>0.86</v>
       </c>
       <c r="G139" t="n">
         <v>0.867</v>
       </c>
       <c r="H139" t="n">
-        <v>0.868</v>
+        <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.879</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -11029,16 +11029,16 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="G155" t="n">
         <v>0.955</v>
       </c>
       <c r="H155" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="I155" t="n">
-        <v>0.979</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="156">
@@ -11621,7 +11621,7 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="G171" t="n">
         <v>0.79</v>
@@ -12213,16 +12213,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.853</v>
+        <v>0.861</v>
       </c>
       <c r="G187" t="n">
         <v>0.865</v>
       </c>
       <c r="H187" t="n">
-        <v>0.868</v>
+        <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.868</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -12805,16 +12805,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.853</v>
+        <v>0.86</v>
       </c>
       <c r="G203" t="n">
-        <v>0.62</v>
+        <v>0.647</v>
       </c>
       <c r="H203" t="n">
-        <v>6.46e-06</v>
+        <v>2.67e-05</v>
       </c>
       <c r="I203" t="n">
-        <v>4.84e-05</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="204">
@@ -13397,16 +13397,16 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="G219" t="n">
-        <v>0.676</v>
+        <v>0.694</v>
       </c>
       <c r="H219" t="n">
-        <v>0.00022</v>
+        <v>0.00047</v>
       </c>
       <c r="I219" t="n">
-        <v>0.00128</v>
+        <v>0.00249</v>
       </c>
     </row>
     <row r="220">
@@ -13989,16 +13989,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="G235" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.617</v>
       </c>
       <c r="H235" t="n">
-        <v>0.004</v>
+        <v>0.0149</v>
       </c>
       <c r="I235" t="n">
-        <v>0.03</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="236">
@@ -14581,16 +14581,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.853</v>
+        <v>0.861</v>
       </c>
       <c r="G251" t="n">
-        <v>0.617</v>
+        <v>0.654</v>
       </c>
       <c r="H251" t="n">
-        <v>3.71e-06</v>
+        <v>2.89e-05</v>
       </c>
       <c r="I251" t="n">
-        <v>2.78e-05</v>
+        <v>0.000217</v>
       </c>
     </row>
     <row r="252">
@@ -15173,16 +15173,16 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.853</v>
+        <v>0.86</v>
       </c>
       <c r="G267" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H267" t="n">
-        <v>1.19e-06</v>
+        <v>3.04e-06</v>
       </c>
       <c r="I267" t="n">
-        <v>1.79e-05</v>
+        <v>4.56e-05</v>
       </c>
     </row>
     <row r="268">
@@ -15765,16 +15765,16 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="G283" t="n">
-        <v>0.648</v>
+        <v>0.662</v>
       </c>
       <c r="H283" t="n">
-        <v>5.96e-05</v>
+        <v>7.41e-05</v>
       </c>
       <c r="I283" t="n">
-        <v>0.000894</v>
+        <v>0.00111</v>
       </c>
     </row>
     <row r="284">
@@ -16357,16 +16357,16 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="G299" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.605</v>
       </c>
       <c r="H299" t="n">
-        <v>0.004</v>
+        <v>0.00946</v>
       </c>
       <c r="I299" t="n">
-        <v>0.03</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="300">
@@ -16949,16 +16949,16 @@
         <v>10</v>
       </c>
       <c r="F315" t="n">
-        <v>0.853</v>
+        <v>0.861</v>
       </c>
       <c r="G315" t="n">
-        <v>0.605</v>
+        <v>0.632</v>
       </c>
       <c r="H315" t="n">
-        <v>1.3e-06</v>
+        <v>3.95e-06</v>
       </c>
       <c r="I315" t="n">
-        <v>1.95e-05</v>
+        <v>5.93e-05</v>
       </c>
     </row>
     <row r="316">
@@ -19918,7 +19918,7 @@
         <v>0.665</v>
       </c>
       <c r="I395" t="n">
-        <v>0.831</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="396">
@@ -21102,7 +21102,7 @@
         <v>0.623</v>
       </c>
       <c r="I427" t="n">
-        <v>0.85</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="428">
@@ -21694,7 +21694,7 @@
         <v>0.5580000000000001</v>
       </c>
       <c r="I443" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="444">
@@ -24062,7 +24062,7 @@
         <v>0.0136</v>
       </c>
       <c r="I507" t="n">
-        <v>0.034</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="508">
@@ -24648,13 +24648,13 @@
         <v>0.787</v>
       </c>
       <c r="G523" t="n">
-        <v>0.753</v>
+        <v>0.78</v>
       </c>
       <c r="H523" t="n">
-        <v>0.583</v>
+        <v>1</v>
       </c>
       <c r="I523" t="n">
-        <v>0.795</v>
+        <v>1</v>
       </c>
     </row>
     <row r="524">
@@ -25240,13 +25240,13 @@
         <v>0.98</v>
       </c>
       <c r="G539" t="n">
-        <v>0.907</v>
+        <v>0.914</v>
       </c>
       <c r="H539" t="n">
-        <v>0.206</v>
+        <v>0.212</v>
       </c>
       <c r="I539" t="n">
-        <v>0.441</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="540">
@@ -25832,13 +25832,13 @@
         <v>0.617</v>
       </c>
       <c r="G555" t="n">
-        <v>0.605</v>
+        <v>0.654</v>
       </c>
       <c r="H555" t="n">
-        <v>1</v>
+        <v>0.744</v>
       </c>
       <c r="I555" t="n">
-        <v>1</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="556">
@@ -26424,13 +26424,13 @@
         <v>0.758</v>
       </c>
       <c r="G571" t="n">
-        <v>0.726</v>
+        <v>0.763</v>
       </c>
       <c r="H571" t="n">
-        <v>0.578</v>
+        <v>1</v>
       </c>
       <c r="I571" t="n">
-        <v>0.6929999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="572">
@@ -27016,13 +27016,13 @@
         <v>0.787</v>
       </c>
       <c r="G587" t="n">
-        <v>0.747</v>
+        <v>0.773</v>
       </c>
       <c r="H587" t="n">
-        <v>0.495</v>
+        <v>0.889</v>
       </c>
       <c r="I587" t="n">
-        <v>0.742</v>
+        <v>1</v>
       </c>
     </row>
     <row r="588">
@@ -27608,13 +27608,13 @@
         <v>0.98</v>
       </c>
       <c r="G603" t="n">
-        <v>0.906</v>
+        <v>0.912</v>
       </c>
       <c r="H603" t="n">
-        <v>0.205</v>
+        <v>0.21</v>
       </c>
       <c r="I603" t="n">
-        <v>0.441</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="604">
@@ -28200,13 +28200,13 @@
         <v>0.617</v>
       </c>
       <c r="G619" t="n">
-        <v>0.593</v>
+        <v>0.642</v>
       </c>
       <c r="H619" t="n">
-        <v>0.872</v>
+        <v>0.871</v>
       </c>
       <c r="I619" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="620">
@@ -28792,13 +28792,13 @@
         <v>0.758</v>
       </c>
       <c r="G635" t="n">
-        <v>0.716</v>
+        <v>0.754</v>
       </c>
       <c r="H635" t="n">
-        <v>0.488</v>
+        <v>1</v>
       </c>
       <c r="I635" t="n">
-        <v>0.6929999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="636">
@@ -31758,7 +31758,7 @@
         <v>0.00511</v>
       </c>
       <c r="I715" t="n">
-        <v>0.0192</v>
+        <v>0.0255</v>
       </c>
     </row>
     <row r="716">
@@ -34120,13 +34120,13 @@
         <v>0.82</v>
       </c>
       <c r="G779" t="n">
-        <v>0.833</v>
+        <v>0.84</v>
       </c>
       <c r="H779" t="n">
-        <v>0.879</v>
+        <v>0.759</v>
       </c>
       <c r="I779" t="n">
-        <v>0.879</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="780">
@@ -34712,13 +34712,13 @@
         <v>0.95</v>
       </c>
       <c r="G795" t="n">
-        <v>0.9</v>
+        <v>0.901</v>
       </c>
       <c r="H795" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I795" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="796">
@@ -35304,13 +35304,13 @@
         <v>0.704</v>
       </c>
       <c r="G811" t="n">
-        <v>0.778</v>
+        <v>0.79</v>
       </c>
       <c r="H811" t="n">
-        <v>0.37</v>
+        <v>0.278</v>
       </c>
       <c r="I811" t="n">
-        <v>0.608</v>
+        <v>0.596</v>
       </c>
     </row>
     <row r="812">
@@ -35896,13 +35896,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="G827" t="n">
-        <v>0.834</v>
+        <v>0.842</v>
       </c>
       <c r="H827" t="n">
-        <v>0.647</v>
+        <v>0.538</v>
       </c>
       <c r="I827" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="828">
@@ -36488,13 +36488,13 @@
         <v>0.82</v>
       </c>
       <c r="G843" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H843" t="n">
-        <v>0.00742</v>
+        <v>0.0212</v>
       </c>
       <c r="I843" t="n">
-        <v>0.0223</v>
+        <v>0.0636</v>
       </c>
     </row>
     <row r="844">
@@ -37080,13 +37080,13 @@
         <v>0.95</v>
       </c>
       <c r="G859" t="n">
-        <v>0.762</v>
+        <v>0.773</v>
       </c>
       <c r="H859" t="n">
-        <v>0.00417</v>
+        <v>0.00488</v>
       </c>
       <c r="I859" t="n">
-        <v>0.0156</v>
+        <v>0.0183</v>
       </c>
     </row>
     <row r="860">
@@ -37672,13 +37672,13 @@
         <v>0.704</v>
       </c>
       <c r="G875" t="n">
-        <v>0.593</v>
+        <v>0.63</v>
       </c>
       <c r="H875" t="n">
-        <v>0.188</v>
+        <v>0.405</v>
       </c>
       <c r="I875" t="n">
-        <v>0.403</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="876">
@@ -38264,13 +38264,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="G891" t="n">
-        <v>0.667</v>
+        <v>0.694</v>
       </c>
       <c r="H891" t="n">
-        <v>0.00723</v>
+        <v>0.0294</v>
       </c>
       <c r="I891" t="n">
-        <v>0.0239</v>
+        <v>0.0735</v>
       </c>
     </row>
     <row r="892">
@@ -38856,13 +38856,13 @@
         <v>0.82</v>
       </c>
       <c r="G907" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H907" t="n">
-        <v>0.00234</v>
+        <v>0.00742</v>
       </c>
       <c r="I907" t="n">
-        <v>0.0117</v>
+        <v>0.0278</v>
       </c>
     </row>
     <row r="908">
@@ -39448,13 +39448,13 @@
         <v>0.95</v>
       </c>
       <c r="G923" t="n">
-        <v>0.708</v>
+        <v>0.72</v>
       </c>
       <c r="H923" t="n">
-        <v>0.000255</v>
+        <v>0.000499</v>
       </c>
       <c r="I923" t="n">
-        <v>0.00128</v>
+        <v>0.00249</v>
       </c>
     </row>
     <row r="924">
@@ -40040,13 +40040,13 @@
         <v>0.704</v>
       </c>
       <c r="G939" t="n">
-        <v>0.63</v>
+        <v>0.667</v>
       </c>
       <c r="H939" t="n">
-        <v>0.405</v>
+        <v>0.735</v>
       </c>
       <c r="I939" t="n">
-        <v>0.608</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="940">
@@ -40632,13 +40632,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="G955" t="n">
-        <v>0.667</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H955" t="n">
-        <v>0.00797</v>
+        <v>0.0234</v>
       </c>
       <c r="I955" t="n">
-        <v>0.0239</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="956">

--- a/rag/eval/results_full150/statistical_tests_full150.xlsx
+++ b/rag/eval/results_full150/statistical_tests_full150.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
